--- a/artfynd/A 19478-2026 artfynd.xlsx
+++ b/artfynd/A 19478-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136114182</v>
       </c>
       <c r="B2" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136114229</v>
       </c>
       <c r="B3" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136114461</v>
       </c>
       <c r="B4" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136114565</v>
       </c>
       <c r="B5" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136115244</v>
       </c>
       <c r="B6" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136114453</v>
       </c>
       <c r="B7" t="n">
-        <v>83294</v>
+        <v>83311</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136114561</v>
       </c>
       <c r="B8" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136114815</v>
       </c>
       <c r="B9" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136114920</v>
       </c>
       <c r="B10" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136115176</v>
       </c>
       <c r="B11" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136114228</v>
       </c>
       <c r="B12" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136114390</v>
       </c>
       <c r="B13" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136114463</v>
       </c>
       <c r="B14" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 19478-2026 artfynd.xlsx
+++ b/artfynd/A 19478-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136114182</v>
       </c>
       <c r="B2" t="n">
-        <v>79523</v>
+        <v>79524</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136114229</v>
       </c>
       <c r="B3" t="n">
-        <v>79523</v>
+        <v>79524</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136114461</v>
       </c>
       <c r="B4" t="n">
-        <v>79523</v>
+        <v>79524</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136114565</v>
       </c>
       <c r="B5" t="n">
-        <v>79523</v>
+        <v>79524</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136115244</v>
       </c>
       <c r="B6" t="n">
-        <v>79523</v>
+        <v>79524</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136114453</v>
       </c>
       <c r="B7" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136114561</v>
       </c>
       <c r="B8" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136114815</v>
       </c>
       <c r="B9" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136114920</v>
       </c>
       <c r="B10" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136115176</v>
       </c>
       <c r="B11" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136114228</v>
       </c>
       <c r="B12" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136114390</v>
       </c>
       <c r="B13" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136114463</v>
       </c>
       <c r="B14" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136112691</v>
       </c>
       <c r="B15" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>136114297</v>
       </c>
       <c r="B16" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>136114342</v>
       </c>
       <c r="B17" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>136114363</v>
       </c>
       <c r="B18" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 19478-2026 artfynd.xlsx
+++ b/artfynd/A 19478-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136114182</v>
       </c>
       <c r="B2" t="n">
-        <v>79524</v>
+        <v>79528</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136114229</v>
       </c>
       <c r="B3" t="n">
-        <v>79524</v>
+        <v>79528</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136114461</v>
       </c>
       <c r="B4" t="n">
-        <v>79524</v>
+        <v>79528</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136114565</v>
       </c>
       <c r="B5" t="n">
-        <v>79524</v>
+        <v>79528</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136115244</v>
       </c>
       <c r="B6" t="n">
-        <v>79524</v>
+        <v>79528</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136114453</v>
       </c>
       <c r="B7" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136114561</v>
       </c>
       <c r="B8" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136114815</v>
       </c>
       <c r="B9" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136114920</v>
       </c>
       <c r="B10" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136115176</v>
       </c>
       <c r="B11" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136114228</v>
       </c>
       <c r="B12" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136114390</v>
       </c>
       <c r="B13" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136114463</v>
       </c>
       <c r="B14" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136112691</v>
       </c>
       <c r="B15" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>136114297</v>
       </c>
       <c r="B16" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>136114342</v>
       </c>
       <c r="B17" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>136114363</v>
       </c>
       <c r="B18" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 19478-2026 artfynd.xlsx
+++ b/artfynd/A 19478-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136114182</v>
       </c>
       <c r="B2" t="n">
-        <v>79528</v>
+        <v>79529</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136114229</v>
       </c>
       <c r="B3" t="n">
-        <v>79528</v>
+        <v>79529</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136114461</v>
       </c>
       <c r="B4" t="n">
-        <v>79528</v>
+        <v>79529</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136114565</v>
       </c>
       <c r="B5" t="n">
-        <v>79528</v>
+        <v>79529</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136115244</v>
       </c>
       <c r="B6" t="n">
-        <v>79528</v>
+        <v>79529</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136114453</v>
       </c>
       <c r="B7" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136114561</v>
       </c>
       <c r="B8" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136114815</v>
       </c>
       <c r="B9" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136114920</v>
       </c>
       <c r="B10" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136115176</v>
       </c>
       <c r="B11" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136114228</v>
       </c>
       <c r="B12" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136114390</v>
       </c>
       <c r="B13" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136114463</v>
       </c>
       <c r="B14" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136112691</v>
       </c>
       <c r="B15" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>136114297</v>
       </c>
       <c r="B16" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>136114342</v>
       </c>
       <c r="B17" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>136114363</v>
       </c>
       <c r="B18" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 19478-2026 artfynd.xlsx
+++ b/artfynd/A 19478-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136114182</v>
       </c>
       <c r="B2" t="n">
-        <v>79529</v>
+        <v>79533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136114229</v>
       </c>
       <c r="B3" t="n">
-        <v>79529</v>
+        <v>79533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136114461</v>
       </c>
       <c r="B4" t="n">
-        <v>79529</v>
+        <v>79533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136114565</v>
       </c>
       <c r="B5" t="n">
-        <v>79529</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136115244</v>
       </c>
       <c r="B6" t="n">
-        <v>79529</v>
+        <v>79533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136114453</v>
       </c>
       <c r="B7" t="n">
-        <v>83317</v>
+        <v>83321</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136114561</v>
       </c>
       <c r="B8" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136114815</v>
       </c>
       <c r="B9" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136114920</v>
       </c>
       <c r="B10" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136115176</v>
       </c>
       <c r="B11" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136114228</v>
       </c>
       <c r="B12" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136114390</v>
       </c>
       <c r="B13" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136114463</v>
       </c>
       <c r="B14" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 19478-2026 artfynd.xlsx
+++ b/artfynd/A 19478-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136114182</v>
       </c>
       <c r="B2" t="n">
-        <v>79533</v>
+        <v>79539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136114229</v>
       </c>
       <c r="B3" t="n">
-        <v>79533</v>
+        <v>79539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136114461</v>
       </c>
       <c r="B4" t="n">
-        <v>79533</v>
+        <v>79539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136114565</v>
       </c>
       <c r="B5" t="n">
-        <v>79533</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136115244</v>
       </c>
       <c r="B6" t="n">
-        <v>79533</v>
+        <v>79539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136114453</v>
       </c>
       <c r="B7" t="n">
-        <v>83321</v>
+        <v>83327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136114561</v>
       </c>
       <c r="B8" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136114815</v>
       </c>
       <c r="B9" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136114920</v>
       </c>
       <c r="B10" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136115176</v>
       </c>
       <c r="B11" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136114228</v>
       </c>
       <c r="B12" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136114390</v>
       </c>
       <c r="B13" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136114463</v>
       </c>
       <c r="B14" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136112691</v>
       </c>
       <c r="B15" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>136114297</v>
       </c>
       <c r="B16" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>136114342</v>
       </c>
       <c r="B17" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>136114363</v>
       </c>
       <c r="B18" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 19478-2026 artfynd.xlsx
+++ b/artfynd/A 19478-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136114182</v>
       </c>
       <c r="B2" t="n">
-        <v>79539</v>
+        <v>79552</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136114229</v>
       </c>
       <c r="B3" t="n">
-        <v>79539</v>
+        <v>79552</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136114461</v>
       </c>
       <c r="B4" t="n">
-        <v>79539</v>
+        <v>79552</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136114565</v>
       </c>
       <c r="B5" t="n">
-        <v>79539</v>
+        <v>79552</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136115244</v>
       </c>
       <c r="B6" t="n">
-        <v>79539</v>
+        <v>79552</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136114453</v>
       </c>
       <c r="B7" t="n">
-        <v>83327</v>
+        <v>83340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136114561</v>
       </c>
       <c r="B8" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136114815</v>
       </c>
       <c r="B9" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136114920</v>
       </c>
       <c r="B10" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136115176</v>
       </c>
       <c r="B11" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136114228</v>
       </c>
       <c r="B12" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136114390</v>
       </c>
       <c r="B13" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136114463</v>
       </c>
       <c r="B14" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136112691</v>
       </c>
       <c r="B15" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>136114297</v>
       </c>
       <c r="B16" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>136114342</v>
       </c>
       <c r="B17" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>136114363</v>
       </c>
       <c r="B18" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 19478-2026 artfynd.xlsx
+++ b/artfynd/A 19478-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136114182</v>
       </c>
       <c r="B2" t="n">
-        <v>79552</v>
+        <v>79553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136114229</v>
       </c>
       <c r="B3" t="n">
-        <v>79552</v>
+        <v>79553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136114461</v>
       </c>
       <c r="B4" t="n">
-        <v>79552</v>
+        <v>79553</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136114565</v>
       </c>
       <c r="B5" t="n">
-        <v>79552</v>
+        <v>79553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136115244</v>
       </c>
       <c r="B6" t="n">
-        <v>79552</v>
+        <v>79553</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136114453</v>
       </c>
       <c r="B7" t="n">
-        <v>83340</v>
+        <v>83341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136114561</v>
       </c>
       <c r="B8" t="n">
-        <v>80589</v>
+        <v>80590</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136114815</v>
       </c>
       <c r="B9" t="n">
-        <v>80589</v>
+        <v>80590</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136114920</v>
       </c>
       <c r="B10" t="n">
-        <v>80589</v>
+        <v>80590</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136115176</v>
       </c>
       <c r="B11" t="n">
-        <v>80589</v>
+        <v>80590</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136114228</v>
       </c>
       <c r="B12" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136114390</v>
       </c>
       <c r="B13" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136114463</v>
       </c>
       <c r="B14" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
